--- a/Result/profitability/2105.xlsx
+++ b/Result/profitability/2105.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.83</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4949999999999999</v>
+        <v>0.465</v>
       </c>
       <c r="N2" t="n">
-        <v>22.605</v>
+        <v>22.67</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5049999999999999</v>
+        <v>0.5225</v>
       </c>
       <c r="N3" t="n">
-        <v>21.7975</v>
+        <v>22.29</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.58</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5349999999999999</v>
+        <v>0.53875</v>
       </c>
       <c r="N4" t="n">
-        <v>21.40875</v>
+        <v>21.65875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5112499999999999</v>
+        <v>0.5362499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>21.18875</v>
+        <v>21.5625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6087499999999999</v>
+        <v>0.60625</v>
       </c>
       <c r="N6" t="n">
-        <v>21.3775</v>
+        <v>21.5575</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>2.56</v>
       </c>
       <c r="M7" t="n">
-        <v>0.86625</v>
+        <v>0.8925000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>22.56875</v>
+        <v>22.8175</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>2.61</v>
       </c>
       <c r="M8" t="n">
-        <v>1.15875</v>
+        <v>1.1475</v>
       </c>
       <c r="N8" t="n">
-        <v>23.87125</v>
+        <v>23.87</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>25190</v>
+      </c>
+      <c r="D75" t="n">
+        <v>18935</v>
+      </c>
+      <c r="E75" t="n">
+        <v>6255</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2515</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.98%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-351</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2164</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1553</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4512499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.22125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.08999999999999997</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1578947368421052</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.01000000000000156</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0004025764895331241</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.714285714285714</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.989999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1369047619047619</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
